--- a/공원현황(홈페이지 발췌).xlsx
+++ b/공원현황(홈페이지 발췌).xlsx
@@ -23,745 +23,790 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="244">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="259">
+  <x:si>
+    <x:t>만촌2동1017-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌3동 862</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌2동1006-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌2동 991-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>야외운동기구 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 4종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌3동870-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물2동1382-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물2동 1376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산1 신매579-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물2동 1348</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산2 시지498-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산1 신매580-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산2 시지137-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산3 매호1329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대등15점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물1동 1302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산1 신매586</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산3 사월동646</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 10종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산2 시지509-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산2 시지487</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산1 신매 598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물1동 1288-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어1동2293</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산3 매호1333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물2동 1367</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대등20점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대등26점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소공원
+(10)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파고라 등 3종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운동기구 등 6점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중동 532-263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>욱수동 19-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근린공원
+(11)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산2동 1247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성생활체육공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 149-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 555-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물동 790-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어린이공원
+(65)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌동 725-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 555-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산2동 1256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌동 1417</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 1종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 2종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어2동 416-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물동 1328-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매호동 1321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌동산 407-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어동 산250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노변동 741 일원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어3동 966-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흔들놀이기구 외 2종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 3종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌1동 656-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흔들놀이기구 외 1종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌3동 852</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산동 1274</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌2동1023-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산1동 1287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산1동 1280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용두</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배수지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관계지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청솔</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달무리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사월</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삼주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동서</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맑음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보람</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유원지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>누리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삼각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나래</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중앙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도담</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상록수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공원명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미조성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연번</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>샛별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>욱수동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>국화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봉선화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진달래</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새마을</x:t>
+  </x:si>
+  <x:si>
+    <x:t>민들레</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호돌이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말뫼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>샛터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지봉</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무궁화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>희망</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에덴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세각단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청소년</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>덕화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>들안길</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>끝동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매579-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매580-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매586</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매594-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매595-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매 598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시지137-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시지487</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시지498-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시지509-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매호1329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매호1333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사월동646</x:t>
+  </x:si>
+  <x:si>
+    <x:t>욱수동19-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동제1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파동 1006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알파시티공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동제2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공원현황</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평의자 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수변공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어린이공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가로공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중동 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대구대공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문화공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두건골공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무학산공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매동 590</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>역사공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성유원지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해충퇴치기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>면적(㎥)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시지동 501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근린공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파동 1012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>들안길꿈나무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대구체육공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>야시골공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매호공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중동127</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화랑공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주요시설</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도시자연공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신매공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 59-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그네 외 2종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노변공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금동 산1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범어공원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파고라등15점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중동171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아랫마을</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 741-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대외2종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운동기구 외 1종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성동3가 130-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금2동 802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상동 400-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌3동874-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성동3가 216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금2동 721</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금2동 750</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 5종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황금2동 882-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만촌3동 1496</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대외5종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대외3종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테니스장, 수성도서관, 주민쉼터, 통일전시관, 산책로, 
+편익시설(화장실, 공중전화, 파고라, 벤치, 체육시설물, 가로등, 휴지통, 주차장, 음수대, 다목적광장, 에어로빅, 배드민턴, 게이트볼 등)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종합놀이대1, 그네1, 정글짐1, 다목적운동장1, 음수대2, 화장실1, 모래장1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>골프연습장, 
+편익시설(화장실2, 음수대1, 벤치88, 체력단련장1, 가로등34, 휴지통33, 주차장3, 파고라3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>편익시설(도로 및 광장 1식, 어린이 놀이터, 조기운동시설외 1종, 화장실1, 노인정1, 파고라1, 휴지통7, 벤치17, 화장실1, 음수대1, 가로등10)</x:t>
+  </x:si>
   <x:si>
     <x:t>어린이회관, 박물관, 운동장, 학생과학관, 궁도장, 노인복지회관, 정구장, 
 편익시설(주차장2, 벤치195, 음수대2, 파고라4, 가로등54, 휴지통17)</x:t>
   </x:si>
   <x:si>
-    <x:t>편익시설(도로 및 광장 1식, 어린이 놀이터, 조기운동시설외 1종, 화장실1, 노인정1, 파고라1, 휴지통7, 벤치17, 화장실1, 음수대1, 가로등10)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테니스장, 수성도서관, 주민쉼터, 통일전시관, 산책로, 
-편익시설(화장실, 공중전화, 파고라, 벤치, 체육시설물, 가로등, 휴지통, 주차장, 음수대, 다목적광장, 에어로빅, 배드민턴, 게이트볼 등)</x:t>
+    <x:t>고산3 매호1330-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대구대공원과 연계하여 조성중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종합경기장 주변으로 조성중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성4가 1090-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산1 신매 595-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고산1 신매 594-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수성4가동 1009-2</x:t>
   </x:si>
   <x:si>
     <x:t>편익시설(도로 및 광장 1식, 어린이놀이터1, 조기운동시설외 1종, 노인정1, 화장실1, 휴지통9, 벤치20, 파고라1, 가로등16)</x:t>
   </x:si>
   <x:si>
-    <x:t>골프연습장, 
-편익시설(화장실2, 음수대1, 벤치88, 체력단련장1, 가로등34, 휴지통33, 주차장3, 파고라3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물2동 1376</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산1 신매579-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물2동 1348</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물2동1382-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물1동 1288-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산1 신매580-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물1동 1302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물2동 1367</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산1 신매586</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산3 사월동646</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 10종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산2 시지487</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산2 시지498-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산3 매호1333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산2 시지509-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산2 시지137-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어1동2293</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산3 매호1329</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산1 신매 598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대등15점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운동기구 등 6점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물동 790-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 149-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대등26점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대등20점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 555-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 555-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중동 532-263</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어린이공원
-(65)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>욱수동 19-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소공원
-(10)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파고라 등 3종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>근린공원
-(11)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성생활체육공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌동 725-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산2동 1247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산2동 1256</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌동 1417</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌동산 407-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어동 산250</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산동 1274</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어2동 416-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노변동 741 일원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물동 1328-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 1종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매호동 1321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어3동 966-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흔들놀이기구 외 2종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌2동1023-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 3종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흔들놀이기구 외 1종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 2종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌1동 656-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌3동 852</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌3동 862</x:t>
-  </x:si>
-  <x:si>
-    <x:t>야외운동기구 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌2동1006-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌2동1017-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌2동 991-8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 4종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌3동870-13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성동3가 130-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금2동 802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금2동 882-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌3동874-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌3동 1496</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성동3가 216</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금2동 721</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금2동 750</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 5종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 400-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대외3종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대외5종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 741-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대외2종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운동기구 외 1종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산1동 1287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산1동 1280</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산2동1184-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산2동1211-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 외 6종</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산1동 1293</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산2동1272-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산1동 1265</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 31-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산1동 1013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성4가동 1009-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산1 신매 595-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산1 신매 594-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성4가 1090-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종합경기장 주변으로 조성중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대구대공원과 연계하여 조성중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산3 매호1330-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물1동1279-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물1동1283-2</x:t>
+    <x:t>편익시설(파고라3, 휴지통11, 벤치44, 음수대1, 가로등17)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>편익시설(화장실1, 파고라3, 휴지통13, 벤치26, 가로등10)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도로 및 광장 1식, 편의시설(등의자 24, 공원등 10, 휴지통3)</x:t>
   </x:si>
   <x:si>
     <x:t>중동 532-263
 (중동 643)</x:t>
   </x:si>
   <x:si>
-    <x:t>종합놀이대1, 그네1, 정글짐1, 다목적운동장1, 음수대2, 화장실1, 모래장1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유원지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배수지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중앙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>삼주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>!!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관계지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보람</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청솔</x:t>
-  </x:si>
-  <x:si>
-    <x:t>누리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맑음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사월</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>삼각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동서</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달무리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도담</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나래</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용두</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미진</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>샛별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>국화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>욱수동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봉선화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진달래</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무열</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새마을</x:t>
-  </x:si>
-  <x:si>
-    <x:t>민들레</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연번</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공원명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미조성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어재</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호돌이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상록수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청소년</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말뫼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에덴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지봉</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>희망</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>끝동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>덕화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무학</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세각단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>들안길</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무궁화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>샛터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>편익시설(파고라3, 휴지통11, 벤치44, 음수대1, 가로등17)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도로 및 광장 1식, 편의시설(등의자 24, 공원등 10, 휴지통3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>편익시설(화장실1, 파고라3, 휴지통13, 벤치26, 가로등10)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동제2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동제1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공원현황</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평의자 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수변공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해충퇴치기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무학산공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>역사공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파동 1006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>면적(㎥)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어린이공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문화공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성유원지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두건골공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가로공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신매동 590</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알파시티공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수성공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중동 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대구대공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주요시설</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대구체육공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도시자연공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>근린공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만촌공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화랑공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지산공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신매공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황금동 산1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노변공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시지동 501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>야시골공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매호공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중동127</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중동171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범어공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범물공원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파동 1012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 343</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상동 59-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파고라등15점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조합놀이대 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아랫마을</x:t>
-  </x:si>
-  <x:si>
-    <x:t>들안길꿈나무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두산동 41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그네 외 2종</x:t>
+    <x:t>지산1동 1293</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물1동1279-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산1동 1265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산2동1211-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조합놀이대 외 6종</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산2동1184-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범물1동1283-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산1동 1013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지산2동1272-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두산동 31-7</x:t>
   </x:si>
   <x:si>
     <x:t>관리사무실 1, 생태연못1, 운동시설물 16 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매호1330-2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1889,7 +1934,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="54.75" customHeight="1">
       <x:c r="A1" s="21" t="s">
-        <x:v>192</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -1899,22 +1944,22 @@
     </x:row>
     <x:row r="2" spans="1:6" s="8" customFormat="1" ht="24.75" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>156</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>147</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>212</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -1922,19 +1967,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>214</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>210</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E3" s="9">
         <x:v>1878637</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -1942,19 +1987,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="22" t="s">
-        <x:v>215</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E4" s="9">
         <x:v>1132458</x:v>
       </x:c>
       <x:c r="F4" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -1963,16 +2008,16 @@
       </x:c>
       <x:c r="B5" s="23"/>
       <x:c r="C5" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E5" s="10">
         <x:v>198268</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -1981,16 +2026,16 @@
       </x:c>
       <x:c r="B6" s="23"/>
       <x:c r="C6" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E6" s="9">
         <x:v>45120</x:v>
       </x:c>
       <x:c r="F6" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -1999,16 +2044,16 @@
       </x:c>
       <x:c r="B7" s="23"/>
       <x:c r="C7" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E7" s="9">
         <x:v>314016</x:v>
       </x:c>
       <x:c r="F7" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2017,16 +2062,16 @@
       </x:c>
       <x:c r="B8" s="23"/>
       <x:c r="C8" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E8" s="9">
         <x:v>4960</x:v>
       </x:c>
       <x:c r="F8" s="6" t="s">
-        <x:v>188</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2035,16 +2080,16 @@
       </x:c>
       <x:c r="B9" s="23"/>
       <x:c r="C9" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E9" s="9">
         <x:v>11572</x:v>
       </x:c>
       <x:c r="F9" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2053,7 +2098,7 @@
       </x:c>
       <x:c r="B10" s="23"/>
       <x:c r="C10" s="3" t="s">
-        <x:v>229</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>48</x:v>
@@ -2062,7 +2107,7 @@
         <x:v>7158</x:v>
       </x:c>
       <x:c r="F10" s="6" t="s">
-        <x:v>189</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2071,16 +2116,16 @@
       </x:c>
       <x:c r="B11" s="23"/>
       <x:c r="C11" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E11" s="9">
         <x:v>9854</x:v>
       </x:c>
       <x:c r="F11" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2089,16 +2134,16 @@
       </x:c>
       <x:c r="B12" s="23"/>
       <x:c r="C12" s="3" t="s">
-        <x:v>221</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E12" s="9">
         <x:v>10454</x:v>
       </x:c>
       <x:c r="F12" s="6" t="s">
-        <x:v>187</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2107,16 +2152,16 @@
       </x:c>
       <x:c r="B13" s="23"/>
       <x:c r="C13" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E13" s="9">
         <x:v>9955</x:v>
       </x:c>
       <x:c r="F13" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2125,16 +2170,16 @@
       </x:c>
       <x:c r="B14" s="24"/>
       <x:c r="C14" s="3" t="s">
-        <x:v>207</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="9">
         <x:v>14117</x:v>
       </x:c>
       <x:c r="F14" s="6" t="s">
-        <x:v>243</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2142,19 +2187,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E15" s="9">
         <x:v>1925700</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2162,19 +2207,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="22" t="s">
-        <x:v>200</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>148</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E16" s="3">
         <x:v>666.10000000000002</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2183,16 +2228,16 @@
       </x:c>
       <x:c r="B17" s="23"/>
       <x:c r="C17" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E17" s="11">
         <x:v>1146.9000000000001</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2201,16 +2246,16 @@
       </x:c>
       <x:c r="B18" s="23"/>
       <x:c r="C18" s="3" t="s">
-        <x:v>139</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E18" s="3">
         <x:v>993.10000000000002</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2219,16 +2264,16 @@
       </x:c>
       <x:c r="B19" s="23"/>
       <x:c r="C19" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E19" s="3">
         <x:v>660.20000000000005</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2237,16 +2282,16 @@
       </x:c>
       <x:c r="B20" s="23"/>
       <x:c r="C20" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E20" s="3">
         <x:v>475.69999999999999</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2255,16 +2300,16 @@
       </x:c>
       <x:c r="B21" s="23"/>
       <x:c r="C21" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E21" s="3">
         <x:v>728.89999999999998</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2273,16 +2318,16 @@
       </x:c>
       <x:c r="B22" s="23"/>
       <x:c r="C22" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E22" s="3">
         <x:v>659.20000000000005</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2291,7 +2336,7 @@
       </x:c>
       <x:c r="B23" s="23"/>
       <x:c r="C23" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>58</x:v>
@@ -2300,7 +2345,7 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2309,16 +2354,16 @@
       </x:c>
       <x:c r="B24" s="23"/>
       <x:c r="C24" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E24" s="11">
         <x:v>2844.9000000000001</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2327,16 +2372,16 @@
       </x:c>
       <x:c r="B25" s="23"/>
       <x:c r="C25" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E25" s="11">
         <x:v>1683.8</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2345,16 +2390,16 @@
       </x:c>
       <x:c r="B26" s="23"/>
       <x:c r="C26" s="3" t="s">
-        <x:v>145</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E26" s="11">
         <x:v>1501.4000000000001</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2363,16 +2408,16 @@
       </x:c>
       <x:c r="B27" s="23"/>
       <x:c r="C27" s="3" t="s">
-        <x:v>151</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E27" s="11">
         <x:v>1634.7</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2381,16 +2426,16 @@
       </x:c>
       <x:c r="B28" s="23"/>
       <x:c r="C28" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E28" s="11">
         <x:v>1650.9000000000001</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2399,16 +2444,16 @@
       </x:c>
       <x:c r="B29" s="23"/>
       <x:c r="C29" s="3" t="s">
-        <x:v>171</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E29" s="11">
         <x:v>1711.7</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2417,16 +2462,16 @@
       </x:c>
       <x:c r="B30" s="23"/>
       <x:c r="C30" s="3" t="s">
-        <x:v>160</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E30" s="11">
         <x:v>1717.7</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2435,16 +2480,16 @@
       </x:c>
       <x:c r="B31" s="23"/>
       <x:c r="C31" s="3" t="s">
-        <x:v>182</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E31" s="11">
         <x:v>1982.2</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2453,16 +2498,16 @@
       </x:c>
       <x:c r="B32" s="23"/>
       <x:c r="C32" s="3" t="s">
-        <x:v>173</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E32" s="11">
         <x:v>1976.5</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2471,16 +2516,16 @@
       </x:c>
       <x:c r="B33" s="23"/>
       <x:c r="C33" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E33" s="11">
         <x:v>1993.0999999999999</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2489,16 +2534,16 @@
       </x:c>
       <x:c r="B34" s="23"/>
       <x:c r="C34" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E34" s="11">
         <x:v>1952.7</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2507,16 +2552,16 @@
       </x:c>
       <x:c r="B35" s="23"/>
       <x:c r="C35" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E35" s="11">
         <x:v>1664.0999999999999</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2525,16 +2570,16 @@
       </x:c>
       <x:c r="B36" s="23"/>
       <x:c r="C36" s="3" t="s">
-        <x:v>161</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E36" s="11">
         <x:v>1984.0999999999999</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2543,16 +2588,16 @@
       </x:c>
       <x:c r="B37" s="23"/>
       <x:c r="C37" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E37" s="11">
         <x:v>1981.8</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2561,16 +2606,16 @@
       </x:c>
       <x:c r="B38" s="23"/>
       <x:c r="C38" s="3" t="s">
-        <x:v>172</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E38" s="11">
         <x:v>2655.1999999999998</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2579,16 +2624,16 @@
       </x:c>
       <x:c r="B39" s="23"/>
       <x:c r="C39" s="3" t="s">
-        <x:v>165</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E39" s="11">
         <x:v>2647.5999999999999</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2597,16 +2642,16 @@
       </x:c>
       <x:c r="B40" s="23"/>
       <x:c r="C40" s="3" t="s">
-        <x:v>181</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E40" s="11">
         <x:v>2643.5999999999999</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2615,16 +2660,16 @@
       </x:c>
       <x:c r="B41" s="23"/>
       <x:c r="C41" s="3" t="s">
-        <x:v>176</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E41" s="11">
         <x:v>1500.7</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2633,16 +2678,16 @@
       </x:c>
       <x:c r="B42" s="23"/>
       <x:c r="C42" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E42" s="11">
         <x:v>2633.4000000000001</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2651,16 +2696,16 @@
       </x:c>
       <x:c r="B43" s="23"/>
       <x:c r="C43" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E43" s="11">
         <x:v>2641.6999999999998</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2669,16 +2714,16 @@
       </x:c>
       <x:c r="B44" s="23"/>
       <x:c r="C44" s="3" t="s">
-        <x:v>174</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E44" s="11">
         <x:v>2653.9000000000001</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2687,16 +2732,16 @@
       </x:c>
       <x:c r="B45" s="23"/>
       <x:c r="C45" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E45" s="11">
         <x:v>1524</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2705,16 +2750,16 @@
       </x:c>
       <x:c r="B46" s="23"/>
       <x:c r="C46" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E46" s="11">
         <x:v>2397</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2723,16 +2768,16 @@
       </x:c>
       <x:c r="B47" s="23"/>
       <x:c r="C47" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E47" s="11">
         <x:v>3315</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2741,16 +2786,16 @@
       </x:c>
       <x:c r="B48" s="23"/>
       <x:c r="C48" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E48" s="11">
         <x:v>1924</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2759,16 +2804,16 @@
       </x:c>
       <x:c r="B49" s="23"/>
       <x:c r="C49" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E49" s="11">
         <x:v>1525.8</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2777,16 +2822,16 @@
       </x:c>
       <x:c r="B50" s="23"/>
       <x:c r="C50" s="3" t="s">
-        <x:v>169</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E50" s="11">
         <x:v>2049</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2795,16 +2840,16 @@
       </x:c>
       <x:c r="B51" s="23"/>
       <x:c r="C51" s="3" t="s">
-        <x:v>167</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E51" s="11">
         <x:v>1502.9000000000001</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2813,16 +2858,16 @@
       </x:c>
       <x:c r="B52" s="23"/>
       <x:c r="C52" s="3" t="s">
-        <x:v>180</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E52" s="11">
         <x:v>2237.4000000000001</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2831,16 +2876,16 @@
       </x:c>
       <x:c r="B53" s="23"/>
       <x:c r="C53" s="3" t="s">
-        <x:v>185</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E53" s="11">
         <x:v>1643.8</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2849,16 +2894,16 @@
       </x:c>
       <x:c r="B54" s="23"/>
       <x:c r="C54" s="3" t="s">
-        <x:v>168</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E54" s="11">
         <x:v>6983.8000000000002</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2867,16 +2912,16 @@
       </x:c>
       <x:c r="B55" s="23"/>
       <x:c r="C55" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E55" s="11">
         <x:v>1493.4000000000001</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2885,16 +2930,16 @@
       </x:c>
       <x:c r="B56" s="23"/>
       <x:c r="C56" s="3" t="s">
-        <x:v>159</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E56" s="11">
         <x:v>1529.0999999999999</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2903,16 +2948,16 @@
       </x:c>
       <x:c r="B57" s="23"/>
       <x:c r="C57" s="3" t="s">
-        <x:v>162</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E57" s="11">
         <x:v>1714.5</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2921,16 +2966,16 @@
       </x:c>
       <x:c r="B58" s="23"/>
       <x:c r="C58" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E58" s="11">
         <x:v>1702.3</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2939,16 +2984,16 @@
       </x:c>
       <x:c r="B59" s="23"/>
       <x:c r="C59" s="3" t="s">
-        <x:v>164</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E59" s="11">
         <x:v>1601.7</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2957,16 +3002,16 @@
       </x:c>
       <x:c r="B60" s="23"/>
       <x:c r="C60" s="3" t="s">
-        <x:v>104</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="11">
         <x:v>1510</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2975,16 +3020,16 @@
       </x:c>
       <x:c r="B61" s="23"/>
       <x:c r="C61" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E61" s="11">
         <x:v>2273.5999999999999</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -2993,16 +3038,16 @@
       </x:c>
       <x:c r="B62" s="23"/>
       <x:c r="C62" s="3" t="s">
-        <x:v>112</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E62" s="11">
         <x:v>3315.9000000000001</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3011,16 +3056,16 @@
       </x:c>
       <x:c r="B63" s="23"/>
       <x:c r="C63" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E63" s="11">
         <x:v>1588.9000000000001</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3029,16 +3074,16 @@
       </x:c>
       <x:c r="B64" s="23"/>
       <x:c r="C64" s="3" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E64" s="11">
         <x:v>4213.6000000000004</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3047,16 +3092,16 @@
       </x:c>
       <x:c r="B65" s="23"/>
       <x:c r="C65" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E65" s="11">
         <x:v>1987.8</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3065,16 +3110,16 @@
       </x:c>
       <x:c r="B66" s="23"/>
       <x:c r="C66" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E66" s="11">
         <x:v>1857.4000000000001</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3083,16 +3128,16 @@
       </x:c>
       <x:c r="B67" s="23"/>
       <x:c r="C67" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E67" s="11">
         <x:v>1451.4000000000001</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3101,16 +3146,16 @@
       </x:c>
       <x:c r="B68" s="23"/>
       <x:c r="C68" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E68" s="11">
         <x:v>2059.4000000000001</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3119,16 +3164,16 @@
       </x:c>
       <x:c r="B69" s="23"/>
       <x:c r="C69" s="3" t="s">
-        <x:v>116</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E69" s="11">
         <x:v>1939.2</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3137,16 +3182,16 @@
       </x:c>
       <x:c r="B70" s="23"/>
       <x:c r="C70" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E70" s="11">
         <x:v>1710.9000000000001</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3155,16 +3200,16 @@
       </x:c>
       <x:c r="B71" s="23"/>
       <x:c r="C71" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E71" s="11">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3173,16 +3218,16 @@
       </x:c>
       <x:c r="B72" s="23"/>
       <x:c r="C72" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E72" s="11">
         <x:v>1568.8</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3191,16 +3236,16 @@
       </x:c>
       <x:c r="B73" s="23"/>
       <x:c r="C73" s="3" t="s">
-        <x:v>133</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E73" s="11">
         <x:v>2955.5999999999999</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3209,16 +3254,16 @@
       </x:c>
       <x:c r="B74" s="23"/>
       <x:c r="C74" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E74" s="11">
         <x:v>2117.6999999999998</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3227,16 +3272,16 @@
       </x:c>
       <x:c r="B75" s="23"/>
       <x:c r="C75" s="3" t="s">
-        <x:v>122</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E75" s="11">
         <x:v>1702.9000000000001</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3245,16 +3290,16 @@
       </x:c>
       <x:c r="B76" s="23"/>
       <x:c r="C76" s="3" t="s">
-        <x:v>130</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E76" s="11">
         <x:v>1582.8</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3263,16 +3308,16 @@
       </x:c>
       <x:c r="B77" s="23"/>
       <x:c r="C77" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E77" s="11">
         <x:v>5671.8000000000002</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3281,16 +3326,16 @@
       </x:c>
       <x:c r="B78" s="23"/>
       <x:c r="C78" s="3" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E78" s="11">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3299,16 +3344,16 @@
       </x:c>
       <x:c r="B79" s="23"/>
       <x:c r="C79" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E79" s="11">
         <x:v>1806.5999999999999</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3317,16 +3362,16 @@
       </x:c>
       <x:c r="B80" s="24"/>
       <x:c r="C80" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E80" s="11">
         <x:v>1802</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3334,19 +3379,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B81" s="22" t="s">
-        <x:v>113</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C81" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E81" s="11">
         <x:v>1441</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3355,16 +3400,16 @@
       </x:c>
       <x:c r="B82" s="23"/>
       <x:c r="C82" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E82" s="11">
         <x:v>2980.9000000000001</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3373,16 +3418,16 @@
       </x:c>
       <x:c r="B83" s="23"/>
       <x:c r="C83" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E83" s="11">
         <x:v>1449.5999999999999</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3391,10 +3436,10 @@
       </x:c>
       <x:c r="B84" s="23"/>
       <x:c r="C84" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E84" s="11">
         <x:v>4313.1000000000004</x:v>
@@ -3409,16 +3454,16 @@
       </x:c>
       <x:c r="B85" s="23"/>
       <x:c r="C85" s="3" t="s">
-        <x:v>191</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E85" s="9">
         <x:v>1270</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3427,16 +3472,16 @@
       </x:c>
       <x:c r="B86" s="23"/>
       <x:c r="C86" s="3" t="s">
-        <x:v>190</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E86" s="9">
         <x:v>1170</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3445,7 +3490,7 @@
       </x:c>
       <x:c r="B87" s="23"/>
       <x:c r="C87" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
         <x:v>32</x:v>
@@ -3454,7 +3499,7 @@
         <x:v>877</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3463,16 +3508,16 @@
       </x:c>
       <x:c r="B88" s="23"/>
       <x:c r="C88" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E88" s="9">
         <x:v>1325</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3481,16 +3526,16 @@
       </x:c>
       <x:c r="B89" s="23"/>
       <x:c r="C89" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E89" s="9">
         <x:v>1058</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:6" ht="24.94999999999999928946" customHeight="1">
@@ -3499,16 +3544,16 @@
       </x:c>
       <x:c r="B90" s="24"/>
       <x:c r="C90" s="3" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E90" s="3">
         <x:v>192</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3519,7 +3564,7 @@
     <x:mergeCell ref="B81:B90"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <x:pageMargins left="0.43305554986000061035" right="0.43305554986000061035" top="0.59041666984558105469" bottom="0.39361110329627990723" header="0.27555555105209350586" footer="0.27555555105209350586"/>
+  <x:pageMargins left="0.4329166710376739502" right="0.4329166710376739502" top="0.59041666984558105469" bottom="0.39347222447395324707" header="0.2754166722297668457" footer="0.2754166722297668457"/>
   <x:pageSetup paperSize="9" scale="75" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -3541,7 +3586,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="54.75" customHeight="1">
       <x:c r="A1" s="21" t="s">
-        <x:v>192</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -3552,26 +3597,26 @@
     </x:row>
     <x:row r="2" spans="1:8" s="8" customFormat="1" ht="24.75" customHeight="1">
       <x:c r="A2" s="14" t="s">
-        <x:v>153</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="14" t="s">
-        <x:v>156</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2" s="14" t="s">
-        <x:v>154</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D2" s="14"/>
       <x:c r="E2" s="14" t="s">
-        <x:v>147</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F2" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G2" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H2" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3590,22 +3635,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="22" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F4" s="12">
         <x:v>1132458</x:v>
       </x:c>
       <x:c r="G4" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3614,19 +3659,19 @@
       </x:c>
       <x:c r="B5" s="23"/>
       <x:c r="C5" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D5" s="16" t="s">
-        <x:v>134</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F5" s="13">
         <x:v>198268</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3635,19 +3680,19 @@
       </x:c>
       <x:c r="B6" s="23"/>
       <x:c r="C6" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F6" s="12">
         <x:v>45120</x:v>
       </x:c>
       <x:c r="G6" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3667,19 +3712,19 @@
       </x:c>
       <x:c r="B8" s="23"/>
       <x:c r="C8" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F8" s="12">
         <x:v>4960</x:v>
       </x:c>
       <x:c r="G8" s="6" t="s">
-        <x:v>188</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3688,19 +3733,19 @@
       </x:c>
       <x:c r="B9" s="23"/>
       <x:c r="C9" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F9" s="12">
         <x:v>11572</x:v>
       </x:c>
       <x:c r="G9" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3709,10 +3754,10 @@
       </x:c>
       <x:c r="B10" s="23"/>
       <x:c r="C10" s="3" t="s">
-        <x:v>229</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>48</x:v>
@@ -3721,7 +3766,7 @@
         <x:v>7158</x:v>
       </x:c>
       <x:c r="G10" s="6" t="s">
-        <x:v>189</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3730,19 +3775,19 @@
       </x:c>
       <x:c r="B11" s="23"/>
       <x:c r="C11" s="19" t="s">
-        <x:v>219</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D11" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E11" s="20" t="s">
-        <x:v>206</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F11" s="12">
         <x:v>9854</x:v>
       </x:c>
       <x:c r="G11" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3751,19 +3796,19 @@
       </x:c>
       <x:c r="B12" s="23"/>
       <x:c r="C12" s="19" t="s">
-        <x:v>221</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D12" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E12" s="20" t="s">
-        <x:v>222</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F12" s="12">
         <x:v>10454</x:v>
       </x:c>
       <x:c r="G12" s="6" t="s">
-        <x:v>187</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3772,19 +3817,19 @@
       </x:c>
       <x:c r="B13" s="23"/>
       <x:c r="C13" s="19" t="s">
-        <x:v>224</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D13" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E13" s="20" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F13" s="12">
         <x:v>9955</x:v>
       </x:c>
       <x:c r="G13" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3793,19 +3838,19 @@
       </x:c>
       <x:c r="B14" s="24"/>
       <x:c r="C14" s="19" t="s">
-        <x:v>207</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D14" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E14" s="20" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F14" s="12">
         <x:v>14117</x:v>
       </x:c>
       <x:c r="G14" s="6" t="s">
-        <x:v>243</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3823,22 +3868,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="22" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>148</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F16" s="12">
         <x:v>666.10000000000002</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3847,19 +3892,19 @@
       </x:c>
       <x:c r="B17" s="23"/>
       <x:c r="C17" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F17" s="12">
         <x:v>1146.9000000000001</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3868,19 +3913,19 @@
       </x:c>
       <x:c r="B18" s="23"/>
       <x:c r="C18" s="3" t="s">
-        <x:v>139</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F18" s="12">
         <x:v>993.10000000000002</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3889,19 +3934,19 @@
       </x:c>
       <x:c r="B19" s="23"/>
       <x:c r="C19" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F19" s="12">
         <x:v>660.20000000000005</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3910,19 +3955,19 @@
       </x:c>
       <x:c r="B20" s="23"/>
       <x:c r="C20" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F20" s="12">
         <x:v>475.69999999999999</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3931,19 +3976,19 @@
       </x:c>
       <x:c r="B21" s="23"/>
       <x:c r="C21" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F21" s="12">
         <x:v>728.89999999999998</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3952,19 +3997,19 @@
       </x:c>
       <x:c r="B22" s="23"/>
       <x:c r="C22" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F22" s="12">
         <x:v>659.20000000000005</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3973,10 +4018,10 @@
       </x:c>
       <x:c r="B23" s="23"/>
       <x:c r="C23" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>58</x:v>
@@ -3985,7 +4030,7 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -3994,19 +4039,19 @@
       </x:c>
       <x:c r="B24" s="23"/>
       <x:c r="C24" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="12">
         <x:v>2844.9000000000001</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4015,19 +4060,19 @@
       </x:c>
       <x:c r="B25" s="23"/>
       <x:c r="C25" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="12">
         <x:v>1683.8</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4036,19 +4081,19 @@
       </x:c>
       <x:c r="B26" s="23"/>
       <x:c r="C26" s="3" t="s">
-        <x:v>145</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F26" s="12">
         <x:v>1501.4000000000001</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4057,19 +4102,19 @@
       </x:c>
       <x:c r="B27" s="23"/>
       <x:c r="C27" s="3" t="s">
-        <x:v>151</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F27" s="12">
         <x:v>1634.7</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4078,19 +4123,19 @@
       </x:c>
       <x:c r="B28" s="23"/>
       <x:c r="C28" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F28" s="12">
         <x:v>1650.9000000000001</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4099,19 +4144,19 @@
       </x:c>
       <x:c r="B29" s="23"/>
       <x:c r="C29" s="3" t="s">
-        <x:v>171</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F29" s="12">
         <x:v>1711.7</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4120,19 +4165,19 @@
       </x:c>
       <x:c r="B30" s="23"/>
       <x:c r="C30" s="3" t="s">
-        <x:v>160</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F30" s="12">
         <x:v>1717.7</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4141,19 +4186,19 @@
       </x:c>
       <x:c r="B31" s="23"/>
       <x:c r="C31" s="3" t="s">
-        <x:v>182</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F31" s="12">
         <x:v>1982.2</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4162,19 +4207,19 @@
       </x:c>
       <x:c r="B32" s="23"/>
       <x:c r="C32" s="3" t="s">
-        <x:v>173</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F32" s="12">
         <x:v>1976.5</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4183,19 +4228,19 @@
       </x:c>
       <x:c r="B33" s="23"/>
       <x:c r="C33" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F33" s="12">
         <x:v>1993.0999999999999</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4204,19 +4249,19 @@
       </x:c>
       <x:c r="B34" s="23"/>
       <x:c r="C34" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F34" s="12">
         <x:v>1952.7</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4225,19 +4270,19 @@
       </x:c>
       <x:c r="B35" s="23"/>
       <x:c r="C35" s="3" t="s">
-        <x:v>183</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F35" s="12">
         <x:v>1664.0999999999999</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4246,19 +4291,19 @@
       </x:c>
       <x:c r="B36" s="23"/>
       <x:c r="C36" s="3" t="s">
-        <x:v>161</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F36" s="12">
         <x:v>1984.0999999999999</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4267,19 +4312,19 @@
       </x:c>
       <x:c r="B37" s="23"/>
       <x:c r="C37" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F37" s="12">
         <x:v>1981.8</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4288,17 +4333,17 @@
       </x:c>
       <x:c r="B38" s="23"/>
       <x:c r="C38" s="3" t="s">
-        <x:v>172</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D38" s="3"/>
       <x:c r="E38" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F38" s="12">
         <x:v>2655.1999999999998</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4307,17 +4352,17 @@
       </x:c>
       <x:c r="B39" s="23"/>
       <x:c r="C39" s="3" t="s">
-        <x:v>165</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D39" s="3"/>
       <x:c r="E39" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F39" s="12">
         <x:v>2647.5999999999999</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4326,17 +4371,17 @@
       </x:c>
       <x:c r="B40" s="23"/>
       <x:c r="C40" s="3" t="s">
-        <x:v>181</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D40" s="3"/>
       <x:c r="E40" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F40" s="12">
         <x:v>2643.5999999999999</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4345,17 +4390,17 @@
       </x:c>
       <x:c r="B41" s="23"/>
       <x:c r="C41" s="3" t="s">
-        <x:v>176</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D41" s="3"/>
       <x:c r="E41" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F41" s="12">
         <x:v>1500.7</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4364,19 +4409,19 @@
       </x:c>
       <x:c r="B42" s="23"/>
       <x:c r="C42" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D42" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F42" s="12">
         <x:v>2633.4000000000001</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4385,19 +4430,19 @@
       </x:c>
       <x:c r="B43" s="23"/>
       <x:c r="C43" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D43" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F43" s="12">
         <x:v>2641.6999999999998</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4406,19 +4451,19 @@
       </x:c>
       <x:c r="B44" s="23"/>
       <x:c r="C44" s="3" t="s">
-        <x:v>174</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F44" s="12">
         <x:v>2653.9000000000001</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4427,19 +4472,19 @@
       </x:c>
       <x:c r="B45" s="23"/>
       <x:c r="C45" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D45" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="F45" s="12">
         <x:v>1524</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4448,19 +4493,19 @@
       </x:c>
       <x:c r="B46" s="23"/>
       <x:c r="C46" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D46" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F46" s="12">
         <x:v>2397</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4469,19 +4514,19 @@
       </x:c>
       <x:c r="B47" s="23"/>
       <x:c r="C47" s="3" t="s">
-        <x:v>175</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D47" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F47" s="12">
         <x:v>3315</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4490,19 +4535,19 @@
       </x:c>
       <x:c r="B48" s="23"/>
       <x:c r="C48" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D48" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F48" s="12">
         <x:v>1924</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4511,19 +4556,19 @@
       </x:c>
       <x:c r="B49" s="23"/>
       <x:c r="C49" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D49" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="F49" s="12">
         <x:v>1525.8</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4532,19 +4577,19 @@
       </x:c>
       <x:c r="B50" s="23"/>
       <x:c r="C50" s="3" t="s">
-        <x:v>169</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F50" s="12">
         <x:v>2049</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4553,19 +4598,19 @@
       </x:c>
       <x:c r="B51" s="23"/>
       <x:c r="C51" s="3" t="s">
-        <x:v>167</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D51" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F51" s="12">
         <x:v>1502.9000000000001</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4574,19 +4619,19 @@
       </x:c>
       <x:c r="B52" s="23"/>
       <x:c r="C52" s="3" t="s">
-        <x:v>180</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D52" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="F52" s="12">
         <x:v>2237.4000000000001</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4595,19 +4640,19 @@
       </x:c>
       <x:c r="B53" s="23"/>
       <x:c r="C53" s="3" t="s">
-        <x:v>185</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D53" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F53" s="12">
         <x:v>1643.8</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4616,19 +4661,19 @@
       </x:c>
       <x:c r="B54" s="23"/>
       <x:c r="C54" s="3" t="s">
-        <x:v>168</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D54" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F54" s="12">
         <x:v>6983.8000000000002</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4637,19 +4682,19 @@
       </x:c>
       <x:c r="B55" s="23"/>
       <x:c r="C55" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D55" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F55" s="12">
         <x:v>1493.4000000000001</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4658,19 +4703,19 @@
       </x:c>
       <x:c r="B56" s="23"/>
       <x:c r="C56" s="3" t="s">
-        <x:v>159</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D56" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F56" s="12">
         <x:v>1529.0999999999999</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4679,19 +4724,19 @@
       </x:c>
       <x:c r="B57" s="23"/>
       <x:c r="C57" s="3" t="s">
-        <x:v>162</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D57" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F57" s="12">
         <x:v>1714.5</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4700,19 +4745,19 @@
       </x:c>
       <x:c r="B58" s="23"/>
       <x:c r="C58" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D58" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="F58" s="12">
         <x:v>1702.3</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4721,19 +4766,19 @@
       </x:c>
       <x:c r="B59" s="23"/>
       <x:c r="C59" s="3" t="s">
-        <x:v>164</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D59" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F59" s="12">
         <x:v>1601.7</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4742,19 +4787,19 @@
       </x:c>
       <x:c r="B60" s="23"/>
       <x:c r="C60" s="3" t="s">
-        <x:v>104</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D60" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F60" s="12">
         <x:v>1510</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4763,19 +4808,19 @@
       </x:c>
       <x:c r="B61" s="23"/>
       <x:c r="C61" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D61" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F61" s="12">
         <x:v>2273.5999999999999</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4784,19 +4829,19 @@
       </x:c>
       <x:c r="B62" s="23"/>
       <x:c r="C62" s="3" t="s">
-        <x:v>112</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D62" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F62" s="12">
         <x:v>3315.9000000000001</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4805,19 +4850,19 @@
       </x:c>
       <x:c r="B63" s="23"/>
       <x:c r="C63" s="3" t="s">
-        <x:v>106</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D63" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F63" s="12">
         <x:v>1588.9000000000001</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4826,19 +4871,19 @@
       </x:c>
       <x:c r="B64" s="23"/>
       <x:c r="C64" s="3" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D64" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F64" s="12">
         <x:v>4213.6000000000004</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4847,19 +4892,19 @@
       </x:c>
       <x:c r="B65" s="23"/>
       <x:c r="C65" s="19" t="s">
-        <x:v>127</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D65" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E65" s="20" t="s">
-        <x:v>6</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F65" s="12">
         <x:v>1987.8</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4868,19 +4913,19 @@
       </x:c>
       <x:c r="B66" s="23"/>
       <x:c r="C66" s="19" t="s">
-        <x:v>117</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D66" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E66" s="20" t="s">
-        <x:v>10</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F66" s="12">
         <x:v>1857.4000000000001</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4889,19 +4934,19 @@
       </x:c>
       <x:c r="B67" s="23"/>
       <x:c r="C67" s="19" t="s">
-        <x:v>123</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D67" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E67" s="20" t="s">
-        <x:v>13</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F67" s="12">
         <x:v>1451.4000000000001</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4910,19 +4955,19 @@
       </x:c>
       <x:c r="B68" s="23"/>
       <x:c r="C68" s="19" t="s">
-        <x:v>124</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D68" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E68" s="20" t="s">
-        <x:v>93</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F68" s="12">
         <x:v>2059.4000000000001</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4931,19 +4976,19 @@
       </x:c>
       <x:c r="B69" s="23"/>
       <x:c r="C69" s="19" t="s">
-        <x:v>116</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D69" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E69" s="20" t="s">
-        <x:v>92</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F69" s="12">
         <x:v>1939.2</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4952,19 +4997,19 @@
       </x:c>
       <x:c r="B70" s="23"/>
       <x:c r="C70" s="19" t="s">
-        <x:v>125</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D70" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E70" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F70" s="12">
         <x:v>1710.9000000000001</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4973,19 +5018,19 @@
       </x:c>
       <x:c r="B71" s="23"/>
       <x:c r="C71" s="19" t="s">
-        <x:v>126</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D71" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E71" s="20" t="s">
-        <x:v>20</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F71" s="12">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -4994,19 +5039,19 @@
       </x:c>
       <x:c r="B72" s="23"/>
       <x:c r="C72" s="19" t="s">
-        <x:v>128</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D72" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E72" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F72" s="12">
         <x:v>1568.8</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5015,19 +5060,19 @@
       </x:c>
       <x:c r="B73" s="23"/>
       <x:c r="C73" s="19" t="s">
-        <x:v>133</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D73" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E73" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F73" s="12">
         <x:v>2955.5999999999999</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5036,19 +5081,19 @@
       </x:c>
       <x:c r="B74" s="23"/>
       <x:c r="C74" s="19" t="s">
-        <x:v>114</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D74" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E74" s="20" t="s">
-        <x:v>19</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F74" s="12">
         <x:v>2117.6999999999998</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5057,19 +5102,19 @@
       </x:c>
       <x:c r="B75" s="23"/>
       <x:c r="C75" s="19" t="s">
-        <x:v>122</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D75" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E75" s="20" t="s">
-        <x:v>22</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F75" s="12">
         <x:v>1702.9000000000001</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5078,19 +5123,19 @@
       </x:c>
       <x:c r="B76" s="23"/>
       <x:c r="C76" s="19" t="s">
-        <x:v>130</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D76" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E76" s="20" t="s">
-        <x:v>18</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F76" s="12">
         <x:v>1582.8</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5099,19 +5144,19 @@
       </x:c>
       <x:c r="B77" s="23"/>
       <x:c r="C77" s="19" t="s">
-        <x:v>118</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D77" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E77" s="20" t="s">
-        <x:v>97</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F77" s="12">
         <x:v>5671.8000000000002</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5120,19 +5165,19 @@
       </x:c>
       <x:c r="B78" s="23"/>
       <x:c r="C78" s="19" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D78" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E78" s="20" t="s">
-        <x:v>14</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F78" s="12">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5141,19 +5186,19 @@
       </x:c>
       <x:c r="B79" s="23"/>
       <x:c r="C79" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D79" s="18" t="s">
-        <x:v>134</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F79" s="12">
         <x:v>1806.5999999999999</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5162,19 +5207,19 @@
       </x:c>
       <x:c r="B80" s="24"/>
       <x:c r="C80" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D80" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F80" s="12">
         <x:v>1802</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5182,20 +5227,20 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B81" s="22" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C81" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D81" s="3"/>
       <x:c r="E81" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F81" s="12">
         <x:v>1441</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5204,17 +5249,17 @@
       </x:c>
       <x:c r="B82" s="23"/>
       <x:c r="C82" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D82" s="3"/>
       <x:c r="E82" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F82" s="12">
         <x:v>2980.9000000000001</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5223,19 +5268,19 @@
       </x:c>
       <x:c r="B83" s="23"/>
       <x:c r="C83" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D83" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="F83" s="12">
         <x:v>1449.5999999999999</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5244,13 +5289,13 @@
       </x:c>
       <x:c r="B84" s="23"/>
       <x:c r="C84" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D84" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F84" s="12">
         <x:v>4313.1000000000004</x:v>
@@ -5265,17 +5310,17 @@
       </x:c>
       <x:c r="B85" s="23"/>
       <x:c r="C85" s="3" t="s">
-        <x:v>191</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D85" s="3"/>
       <x:c r="E85" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="12">
         <x:v>1270</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5284,17 +5329,17 @@
       </x:c>
       <x:c r="B86" s="23"/>
       <x:c r="C86" s="3" t="s">
-        <x:v>190</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D86" s="3"/>
       <x:c r="E86" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F86" s="12">
         <x:v>1170</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5303,19 +5348,19 @@
       </x:c>
       <x:c r="B87" s="23"/>
       <x:c r="C87" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D87" s="3" t="s">
-        <x:v>184</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F87" s="12">
         <x:v>877</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9" ht="24.94999999999999928946" customHeight="1">
@@ -5324,22 +5369,22 @@
       </x:c>
       <x:c r="B88" s="23"/>
       <x:c r="C88" s="3" t="s">
-        <x:v>163</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D88" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F88" s="12">
         <x:v>1325</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="I88" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5348,19 +5393,19 @@
       </x:c>
       <x:c r="B89" s="23"/>
       <x:c r="C89" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D89" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F89" s="12">
         <x:v>1058</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7" ht="24.94999999999999928946" customHeight="1">
@@ -5369,19 +5414,19 @@
       </x:c>
       <x:c r="B90" s="24"/>
       <x:c r="C90" s="19" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D90" s="19" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E90" s="20" t="s">
-        <x:v>34</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F90" s="12">
         <x:v>192</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:4">
@@ -5389,13 +5434,13 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B91" s="8" t="s">
-        <x:v>203</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C91" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D91" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:4">
@@ -5403,13 +5448,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B92" s="8" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C92" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D92" s="8" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:4">
@@ -5417,13 +5462,13 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B93" s="8" t="s">
-        <x:v>196</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C93" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D93" s="8" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:5">
@@ -5431,16 +5476,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B94" s="8" t="s">
-        <x:v>204</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C94" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D94" s="8" t="s">
-        <x:v>137</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E94" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:1">
@@ -5460,7 +5505,7 @@
     </x:row>
     <x:row r="100" spans="2:3">
       <x:c r="B100" s="8" t="s">
-        <x:v>194</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C100" s="8">
         <x:v>1</x:v>
@@ -5473,7 +5518,7 @@
     </x:row>
     <x:row r="102" spans="2:3">
       <x:c r="B102" s="8" t="s">
-        <x:v>201</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C102" s="8">
         <x:v>1</x:v>
@@ -5481,7 +5526,7 @@
     </x:row>
     <x:row r="103" spans="2:3">
       <x:c r="B103" s="8" t="s">
-        <x:v>197</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C103" s="8">
         <x:v>1</x:v>
@@ -5489,7 +5534,7 @@
     </x:row>
     <x:row r="104" spans="2:3">
       <x:c r="B104" s="8" t="s">
-        <x:v>205</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C104" s="8">
         <x:v>1</x:v>
@@ -5497,7 +5542,7 @@
     </x:row>
     <x:row r="105" spans="2:3">
       <x:c r="B105" s="8" t="s">
-        <x:v>202</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C105" s="8">
         <x:v>1</x:v>
@@ -5505,7 +5550,7 @@
     </x:row>
     <x:row r="106" spans="2:3">
       <x:c r="B106" s="8" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C106" s="8">
         <x:v>2</x:v>
@@ -5520,7 +5565,7 @@
     <x:mergeCell ref="B81:B90"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <x:pageMargins left="0.43305554986000061035" right="0.43305554986000061035" top="0.59041666984558105469" bottom="0.39361110329627990723" header="0.27555555105209350586" footer="0.27555555105209350586"/>
+  <x:pageMargins left="0.4329166710376739502" right="0.4329166710376739502" top="0.59041666984558105469" bottom="0.39347222447395324707" header="0.2754166722297668457" footer="0.2754166722297668457"/>
   <x:pageSetup paperSize="9" scale="75" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>